--- a/public/question-import-template.xlsx
+++ b/public/question-import-template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,16 @@
           <t>Sort Order</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -505,6 +515,16 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Working capital terminology</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -542,6 +562,16 @@
       </c>
       <c r="H3" t="n">
         <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Revenue drivers</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/public/question-import-template.xlsx
+++ b/public/question-import-template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -467,16 +467,6 @@
           <t>Sort Order</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Skill</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -515,16 +505,6 @@
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Working capital terminology</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,16 +542,6 @@
       </c>
       <c r="H3" t="n">
         <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Revenue drivers</t>
-        </is>
       </c>
     </row>
   </sheetData>
